--- a/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre13.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre13.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="BG_FPS" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Scenario</t>
   </si>
@@ -71,39 +71,6 @@
   </si>
   <si>
     <t>Quantity</t>
-  </si>
-  <si>
-    <t>Optimized</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>Punjab</t>
-  </si>
-  <si>
-    <t>SRI MUKTSAR SAHIB</t>
-  </si>
-  <si>
-    <t>Malout</t>
-  </si>
-  <si>
-    <t>KARAM PATTI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>Depot</t>
-  </si>
-  <si>
-    <t>agah</t>
-  </si>
-  <si>
-    <t>FAZILKA</t>
-  </si>
-  <si>
-    <t>Abohar</t>
-  </si>
-  <si>
-    <t>Paddy</t>
   </si>
 </sst>
 </file>
@@ -461,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -523,65 +490,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2">
-        <v>1660</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>30.2397029</v>
-      </c>
-      <c r="I2">
-        <v>74.2953411</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2">
-        <v>407</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2">
-        <v>30.126927</v>
-      </c>
-      <c r="Q2">
-        <v>74.161942</v>
-      </c>
-      <c r="R2" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2">
-        <v>15621</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre13.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre13.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="BG_FPS" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="56">
   <si>
     <t>Scenario</t>
   </si>
@@ -71,6 +71,117 @@
   </si>
   <si>
     <t>Quantity</t>
+  </si>
+  <si>
+    <t>Optimized</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Punjab</t>
+  </si>
+  <si>
+    <t>JALANDHAR</t>
+  </si>
+  <si>
+    <t>AMRITSAR</t>
+  </si>
+  <si>
+    <t>SRI MUKTSAR SAHIB</t>
+  </si>
+  <si>
+    <t>TARN TARAN</t>
+  </si>
+  <si>
+    <t>JALANDHAR CITY</t>
+  </si>
+  <si>
+    <t>Malout</t>
+  </si>
+  <si>
+    <t>ATTARI</t>
+  </si>
+  <si>
+    <t>NAUSHEHRA PANNUAN</t>
+  </si>
+  <si>
+    <t>BHIKHIWIND</t>
+  </si>
+  <si>
+    <t>CHOGAWAN</t>
+  </si>
+  <si>
+    <t>JANDIALA</t>
+  </si>
+  <si>
+    <t>MEHTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JALANDHAR CITY  </t>
+  </si>
+  <si>
+    <t>BHAGTANWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHHEHRTA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KARAM PATTI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BASARKE GILLAN GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHOTIYA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KANG GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHALRA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHASSA BAZAAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHIALA KHURD GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>RAJA SANSI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>TARSIKKA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JALAL USMA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>Depot</t>
+  </si>
+  <si>
+    <t>agah</t>
+  </si>
+  <si>
+    <t>FAZILKA</t>
+  </si>
+  <si>
+    <t>Vallah</t>
+  </si>
+  <si>
+    <t>Bhagtanwala</t>
+  </si>
+  <si>
+    <t>Verka</t>
+  </si>
+  <si>
+    <t>Chhehrata</t>
+  </si>
+  <si>
+    <t>Abohar</t>
+  </si>
+  <si>
+    <t>Paddy</t>
   </si>
 </sst>
 </file>
@@ -428,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -490,6 +601,1304 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2">
+        <v>1066</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2">
+        <v>31.342037</v>
+      </c>
+      <c r="I2">
+        <v>75.56746099999999</v>
+      </c>
+      <c r="J2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2">
+        <v>33</v>
+      </c>
+      <c r="L2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2">
+        <v>31.3844</v>
+      </c>
+      <c r="Q2">
+        <v>75.55336</v>
+      </c>
+      <c r="R2" t="s">
+        <v>55</v>
+      </c>
+      <c r="S2">
+        <v>65710</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3">
+        <v>31.60353941</v>
+      </c>
+      <c r="I3">
+        <v>74.86858903</v>
+      </c>
+      <c r="J3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P3">
+        <v>31.57114</v>
+      </c>
+      <c r="Q3">
+        <v>74.8843</v>
+      </c>
+      <c r="R3" t="s">
+        <v>55</v>
+      </c>
+      <c r="S3">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4">
+        <v>31.60353941</v>
+      </c>
+      <c r="I4">
+        <v>74.86858903</v>
+      </c>
+      <c r="J4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4">
+        <v>42</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s">
+        <v>51</v>
+      </c>
+      <c r="P4">
+        <v>31.64602</v>
+      </c>
+      <c r="Q4">
+        <v>74.85684000000001</v>
+      </c>
+      <c r="R4" t="s">
+        <v>55</v>
+      </c>
+      <c r="S4">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5">
+        <v>31.60353941</v>
+      </c>
+      <c r="I5">
+        <v>74.86858903</v>
+      </c>
+      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P5">
+        <v>31.5646079</v>
+      </c>
+      <c r="Q5">
+        <v>74.8878672</v>
+      </c>
+      <c r="R5" t="s">
+        <v>55</v>
+      </c>
+      <c r="S5">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6">
+        <v>31.60353941</v>
+      </c>
+      <c r="I6">
+        <v>74.86858903</v>
+      </c>
+      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6">
+        <v>31.580623</v>
+      </c>
+      <c r="Q6">
+        <v>74.8949673</v>
+      </c>
+      <c r="R6" t="s">
+        <v>55</v>
+      </c>
+      <c r="S6">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7">
+        <v>31.60353941</v>
+      </c>
+      <c r="I7">
+        <v>74.86858903</v>
+      </c>
+      <c r="J7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" t="s">
+        <v>51</v>
+      </c>
+      <c r="P7">
+        <v>31.582043</v>
+      </c>
+      <c r="Q7">
+        <v>74.8871613</v>
+      </c>
+      <c r="R7" t="s">
+        <v>55</v>
+      </c>
+      <c r="S7">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8">
+        <v>31.63383417</v>
+      </c>
+      <c r="I8">
+        <v>74.78424411</v>
+      </c>
+      <c r="J8" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" t="s">
+        <v>52</v>
+      </c>
+      <c r="P8">
+        <v>31.6603418</v>
+      </c>
+      <c r="Q8">
+        <v>74.78764959999999</v>
+      </c>
+      <c r="R8" t="s">
+        <v>55</v>
+      </c>
+      <c r="S8">
+        <v>19258.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9">
+        <v>31.63383417</v>
+      </c>
+      <c r="I9">
+        <v>74.78424411</v>
+      </c>
+      <c r="J9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9">
+        <v>24</v>
+      </c>
+      <c r="L9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" t="s">
+        <v>53</v>
+      </c>
+      <c r="P9">
+        <v>31.60898</v>
+      </c>
+      <c r="Q9">
+        <v>74.78771999999999</v>
+      </c>
+      <c r="R9" t="s">
+        <v>55</v>
+      </c>
+      <c r="S9">
+        <v>52445.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10">
+        <v>1660</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10">
+        <v>30.2397029</v>
+      </c>
+      <c r="I10">
+        <v>74.2953411</v>
+      </c>
+      <c r="J10" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10">
+        <v>407</v>
+      </c>
+      <c r="L10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s">
+        <v>49</v>
+      </c>
+      <c r="O10" t="s">
+        <v>54</v>
+      </c>
+      <c r="P10">
+        <v>30.126927</v>
+      </c>
+      <c r="Q10">
+        <v>74.161942</v>
+      </c>
+      <c r="R10" t="s">
+        <v>55</v>
+      </c>
+      <c r="S10">
+        <v>15621</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11">
+        <v>31.5759564</v>
+      </c>
+      <c r="I11">
+        <v>74.77089024999999</v>
+      </c>
+      <c r="J11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11">
+        <v>24</v>
+      </c>
+      <c r="L11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" t="s">
+        <v>53</v>
+      </c>
+      <c r="P11">
+        <v>31.60898</v>
+      </c>
+      <c r="Q11">
+        <v>74.78771999999999</v>
+      </c>
+      <c r="R11" t="s">
+        <v>55</v>
+      </c>
+      <c r="S11">
+        <v>6721</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12">
+        <v>31.5759564</v>
+      </c>
+      <c r="I12">
+        <v>74.77089024999999</v>
+      </c>
+      <c r="J12" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12">
+        <v>26</v>
+      </c>
+      <c r="L12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" t="s">
+        <v>53</v>
+      </c>
+      <c r="P12">
+        <v>31.598156</v>
+      </c>
+      <c r="Q12">
+        <v>74.784094</v>
+      </c>
+      <c r="R12" t="s">
+        <v>55</v>
+      </c>
+      <c r="S12">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13">
+        <v>2139</v>
+      </c>
+      <c r="G13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13">
+        <v>31.3723382</v>
+      </c>
+      <c r="I13">
+        <v>75.0068966</v>
+      </c>
+      <c r="J13" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13">
+        <v>40</v>
+      </c>
+      <c r="L13" t="s">
+        <v>48</v>
+      </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13" t="s">
+        <v>50</v>
+      </c>
+      <c r="P13">
+        <v>31.43316</v>
+      </c>
+      <c r="Q13">
+        <v>75.00457</v>
+      </c>
+      <c r="R13" t="s">
+        <v>55</v>
+      </c>
+      <c r="S13">
+        <v>91350</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14">
+        <v>2151</v>
+      </c>
+      <c r="G14" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14">
+        <v>31.4581661</v>
+      </c>
+      <c r="I14">
+        <v>75.0448694</v>
+      </c>
+      <c r="J14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K14">
+        <v>40</v>
+      </c>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" t="s">
+        <v>50</v>
+      </c>
+      <c r="P14">
+        <v>31.43316</v>
+      </c>
+      <c r="Q14">
+        <v>75.00457</v>
+      </c>
+      <c r="R14" t="s">
+        <v>55</v>
+      </c>
+      <c r="S14">
+        <v>33650</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15">
+        <v>2153</v>
+      </c>
+      <c r="G15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15">
+        <v>31.3953454</v>
+      </c>
+      <c r="I15">
+        <v>74.6222925</v>
+      </c>
+      <c r="J15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s">
+        <v>23</v>
+      </c>
+      <c r="O15" t="s">
+        <v>53</v>
+      </c>
+      <c r="P15">
+        <v>31.45335</v>
+      </c>
+      <c r="Q15">
+        <v>74.46541999999999</v>
+      </c>
+      <c r="R15" t="s">
+        <v>55</v>
+      </c>
+      <c r="S15">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16">
+        <v>2153</v>
+      </c>
+      <c r="G16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16">
+        <v>31.3953454</v>
+      </c>
+      <c r="I16">
+        <v>74.6222925</v>
+      </c>
+      <c r="J16" t="s">
+        <v>47</v>
+      </c>
+      <c r="K16">
+        <v>4</v>
+      </c>
+      <c r="L16" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" t="s">
+        <v>23</v>
+      </c>
+      <c r="O16" t="s">
+        <v>52</v>
+      </c>
+      <c r="P16">
+        <v>31.45335</v>
+      </c>
+      <c r="Q16">
+        <v>74.46541999999999</v>
+      </c>
+      <c r="R16" t="s">
+        <v>55</v>
+      </c>
+      <c r="S16">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17">
+        <v>2153</v>
+      </c>
+      <c r="G17" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17">
+        <v>31.3953454</v>
+      </c>
+      <c r="I17">
+        <v>74.6222925</v>
+      </c>
+      <c r="J17" t="s">
+        <v>47</v>
+      </c>
+      <c r="K17">
+        <v>9</v>
+      </c>
+      <c r="L17" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" t="s">
+        <v>23</v>
+      </c>
+      <c r="O17" t="s">
+        <v>51</v>
+      </c>
+      <c r="P17">
+        <v>31.45335</v>
+      </c>
+      <c r="Q17">
+        <v>74.46541999999999</v>
+      </c>
+      <c r="R17" t="s">
+        <v>55</v>
+      </c>
+      <c r="S17">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18">
+        <v>21</v>
+      </c>
+      <c r="G18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18">
+        <v>31.62101209</v>
+      </c>
+      <c r="I18">
+        <v>74.73375702</v>
+      </c>
+      <c r="J18" t="s">
+        <v>47</v>
+      </c>
+      <c r="K18">
+        <v>24</v>
+      </c>
+      <c r="L18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O18" t="s">
+        <v>53</v>
+      </c>
+      <c r="P18">
+        <v>31.60898</v>
+      </c>
+      <c r="Q18">
+        <v>74.78771999999999</v>
+      </c>
+      <c r="R18" t="s">
+        <v>55</v>
+      </c>
+      <c r="S18">
+        <v>833.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19">
+        <v>31.62101209</v>
+      </c>
+      <c r="I19">
+        <v>74.73375702</v>
+      </c>
+      <c r="J19" t="s">
+        <v>47</v>
+      </c>
+      <c r="K19">
+        <v>25</v>
+      </c>
+      <c r="L19" t="s">
+        <v>48</v>
+      </c>
+      <c r="M19" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" t="s">
+        <v>53</v>
+      </c>
+      <c r="P19">
+        <v>31.60898</v>
+      </c>
+      <c r="Q19">
+        <v>74.78771999999999</v>
+      </c>
+      <c r="R19" t="s">
+        <v>55</v>
+      </c>
+      <c r="S19">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20">
+        <v>28</v>
+      </c>
+      <c r="G20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20">
+        <v>31.6812548</v>
+      </c>
+      <c r="I20">
+        <v>74.7251109</v>
+      </c>
+      <c r="J20" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20">
+        <v>22</v>
+      </c>
+      <c r="L20" t="s">
+        <v>48</v>
+      </c>
+      <c r="M20" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" t="s">
+        <v>23</v>
+      </c>
+      <c r="O20" t="s">
+        <v>52</v>
+      </c>
+      <c r="P20">
+        <v>31.6603418</v>
+      </c>
+      <c r="Q20">
+        <v>74.78764959999999</v>
+      </c>
+      <c r="R20" t="s">
+        <v>55</v>
+      </c>
+      <c r="S20">
+        <v>107242.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21">
+        <v>31</v>
+      </c>
+      <c r="G21" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21">
+        <v>31.7247824</v>
+      </c>
+      <c r="I21">
+        <v>74.8026407</v>
+      </c>
+      <c r="J21" t="s">
+        <v>47</v>
+      </c>
+      <c r="K21">
+        <v>22</v>
+      </c>
+      <c r="L21" t="s">
+        <v>48</v>
+      </c>
+      <c r="M21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" t="s">
+        <v>52</v>
+      </c>
+      <c r="P21">
+        <v>31.6603418</v>
+      </c>
+      <c r="Q21">
+        <v>74.78764959999999</v>
+      </c>
+      <c r="R21" t="s">
+        <v>55</v>
+      </c>
+      <c r="S21">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22">
+        <v>39</v>
+      </c>
+      <c r="G22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22">
+        <v>31.63465</v>
+      </c>
+      <c r="I22">
+        <v>75.136478</v>
+      </c>
+      <c r="J22" t="s">
+        <v>47</v>
+      </c>
+      <c r="K22">
+        <v>32</v>
+      </c>
+      <c r="L22" t="s">
+        <v>48</v>
+      </c>
+      <c r="M22" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O22" t="s">
+        <v>53</v>
+      </c>
+      <c r="P22">
+        <v>31.61865</v>
+      </c>
+      <c r="Q22">
+        <v>75.173281</v>
+      </c>
+      <c r="R22" t="s">
+        <v>55</v>
+      </c>
+      <c r="S22">
+        <v>59553</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23">
+        <v>49</v>
+      </c>
+      <c r="G23" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23">
+        <v>31.6557769</v>
+      </c>
+      <c r="I23">
+        <v>75.20907029999999</v>
+      </c>
+      <c r="J23" t="s">
+        <v>47</v>
+      </c>
+      <c r="K23">
+        <v>32</v>
+      </c>
+      <c r="L23" t="s">
+        <v>48</v>
+      </c>
+      <c r="M23" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" t="s">
+        <v>23</v>
+      </c>
+      <c r="O23" t="s">
+        <v>53</v>
+      </c>
+      <c r="P23">
+        <v>31.61865</v>
+      </c>
+      <c r="Q23">
+        <v>75.173281</v>
+      </c>
+      <c r="R23" t="s">
+        <v>55</v>
+      </c>
+      <c r="S23">
+        <v>5447</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
